--- a/results.xlsx
+++ b/results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AAlonzo\Documents\UniTec\semester 5\Analysis and Design of Advanced Algorithms\activity3.2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\OneDrive\Documentos\Activity3.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68E12224-683E-4D2D-936B-E89C6CBFEDF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00B3D42-0DCD-4E61-8111-492246F40F85}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{80091D4D-D187-4FE6-BA1D-5A1268D7778A}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" xr2:uid="{80091D4D-D187-4FE6-BA1D-5A1268D7778A}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -20,23 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="5">
   <si>
     <t>Number of cities</t>
   </si>
@@ -46,12 +35,18 @@
   <si>
     <t xml:space="preserve"> </t>
   </si>
+  <si>
+    <t>MST-TSP</t>
+  </si>
+  <si>
+    <t>Cheapest Link-TSP</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -65,6 +60,13 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -158,46 +160,70 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -532,55 +558,92 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFDDFCA7-22C7-463A-B228-F7BE813B58FC}">
-  <dimension ref="A1:M19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:V20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" customWidth="1"/>
-    <col min="2" max="10" width="8.109375" customWidth="1"/>
+    <col min="1" max="1" width="15.375" customWidth="1"/>
+    <col min="2" max="10" width="8.125" customWidth="1"/>
+    <col min="13" max="13" width="8.25" style="21" customWidth="1"/>
+    <col min="14" max="14" width="7.125" customWidth="1"/>
+    <col min="15" max="15" width="4.375" customWidth="1"/>
+    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="17" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="6.625" customWidth="1"/>
+    <col min="19" max="19" width="5.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="30">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="3" t="s">
+      <c r="C1" s="15"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="3" t="s">
+      <c r="F1" s="15"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="15"/>
+      <c r="J1" s="16"/>
+      <c r="M1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="5"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="6">
+      <c r="O1" s="24"/>
+      <c r="P1" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q1" s="24"/>
+      <c r="R1" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="S1" s="24"/>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" s="12">
         <v>10</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="3">
         <v>10</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="3">
         <v>15</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="4">
         <v>5</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="8"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="4"/>
+      <c r="M2" s="19">
+        <v>10</v>
+      </c>
+      <c r="N2" s="17">
+        <v>3670198</v>
+      </c>
+      <c r="O2" s="18"/>
+      <c r="P2" s="17">
+        <v>3472260</v>
+      </c>
+      <c r="Q2" s="18"/>
+      <c r="R2" s="17">
+        <v>2340689</v>
+      </c>
+      <c r="S2" s="18"/>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3" s="12"/>
       <c r="B3" s="9">
         <f>SUM(B2:D2)/COUNT(B2:D2)</f>
         <v>10</v>
@@ -599,27 +662,56 @@
       </c>
       <c r="I3" s="10"/>
       <c r="J3" s="11"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="12">
+      <c r="M3" s="19">
         <v>50</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="14"/>
+      <c r="N3" s="17">
+        <v>6327727</v>
+      </c>
+      <c r="O3" s="18"/>
+      <c r="P3" s="17">
+        <v>5945171</v>
+      </c>
+      <c r="Q3" s="18"/>
+      <c r="R3" s="17">
+        <v>3980123</v>
+      </c>
+      <c r="S3" s="18"/>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" s="13">
+        <v>50</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="6"/>
       <c r="L4" t="s">
         <v>2</v>
       </c>
-      <c r="M4" s="15"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="12"/>
+      <c r="M4" s="20">
+        <v>100</v>
+      </c>
+      <c r="N4" s="17">
+        <v>8667736</v>
+      </c>
+      <c r="O4" s="18"/>
+      <c r="P4" s="17">
+        <v>7640063</v>
+      </c>
+      <c r="Q4" s="18"/>
+      <c r="R4" s="17">
+        <v>5559666</v>
+      </c>
+      <c r="S4" s="18"/>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" s="13"/>
       <c r="B5" s="9" t="e">
         <f>SUM(B4:D4)/COUNT(B4:D4)</f>
         <v>#DIV/0!</v>
@@ -638,24 +730,54 @@
       </c>
       <c r="I5" s="10"/>
       <c r="J5" s="11"/>
-      <c r="L5" s="15"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="6">
+      <c r="L5" s="7"/>
+      <c r="M5" s="19">
+        <v>200</v>
+      </c>
+      <c r="N5" s="17">
+        <v>11248409</v>
+      </c>
+      <c r="O5" s="18"/>
+      <c r="P5" s="17">
+        <v>10834004</v>
+      </c>
+      <c r="Q5" s="18"/>
+      <c r="R5" s="17">
+        <v>7388240</v>
+      </c>
+      <c r="S5" s="18"/>
+    </row>
+    <row r="6" spans="1:19">
+      <c r="A6" s="12">
         <v>100</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="8"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="4"/>
+      <c r="M6" s="19">
+        <v>400</v>
+      </c>
+      <c r="N6" s="17">
+        <v>16092556</v>
+      </c>
+      <c r="O6" s="18"/>
+      <c r="P6" s="17">
+        <v>14563257</v>
+      </c>
+      <c r="Q6" s="18"/>
+      <c r="R6" s="17">
+        <v>9914009</v>
+      </c>
+      <c r="S6" s="18"/>
+    </row>
+    <row r="7" spans="1:19">
+      <c r="A7" s="12"/>
       <c r="B7" s="9" t="e">
         <f>SUM(B6:D6)/COUNT(B6:D6)</f>
         <v>#DIV/0!</v>
@@ -674,23 +796,53 @@
       </c>
       <c r="I7" s="10"/>
       <c r="J7" s="11"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="12">
+      <c r="M7" s="19">
+        <v>600</v>
+      </c>
+      <c r="N7" s="17">
+        <v>19703651</v>
+      </c>
+      <c r="O7" s="18"/>
+      <c r="P7" s="17">
+        <v>17598642</v>
+      </c>
+      <c r="Q7" s="18"/>
+      <c r="R7" s="17">
+        <v>12143263</v>
+      </c>
+      <c r="S7" s="18"/>
+    </row>
+    <row r="8" spans="1:19">
+      <c r="A8" s="13">
         <v>200</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="14"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="12"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="6"/>
+      <c r="M8" s="19">
+        <v>800</v>
+      </c>
+      <c r="N8" s="17">
+        <v>21022945</v>
+      </c>
+      <c r="O8" s="18"/>
+      <c r="P8" s="17">
+        <v>19871304</v>
+      </c>
+      <c r="Q8" s="18"/>
+      <c r="R8" s="17">
+        <v>14216831</v>
+      </c>
+      <c r="S8" s="18"/>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="A9" s="13"/>
       <c r="B9" s="9" t="e">
         <f>SUM(B8:D8)/COUNT(B8:D8)</f>
         <v>#DIV/0!</v>
@@ -709,23 +861,38 @@
       </c>
       <c r="I9" s="10"/>
       <c r="J9" s="11"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="6">
+      <c r="M9" s="19">
+        <v>1000</v>
+      </c>
+      <c r="N9" s="17">
+        <v>24648527</v>
+      </c>
+      <c r="O9" s="18"/>
+      <c r="P9" s="17">
+        <v>21705718</v>
+      </c>
+      <c r="Q9" s="18"/>
+      <c r="R9" s="17">
+        <v>15904768</v>
+      </c>
+      <c r="S9" s="18"/>
+    </row>
+    <row r="10" spans="1:19">
+      <c r="A10" s="12">
         <v>400</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="8"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" spans="1:19">
+      <c r="A11" s="12"/>
       <c r="B11" s="9" t="e">
         <f>SUM(B10:D10)/COUNT(B10:D10)</f>
         <v>#DIV/0!</v>
@@ -745,22 +912,22 @@
       <c r="I11" s="10"/>
       <c r="J11" s="11"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="12">
+    <row r="12" spans="1:19">
+      <c r="A12" s="13">
         <v>600</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="14"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="12"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="6"/>
+    </row>
+    <row r="13" spans="1:19">
+      <c r="A13" s="13"/>
       <c r="B13" s="9" t="e">
         <f>SUM(B12:D12)/COUNT(B12:D12)</f>
         <v>#DIV/0!</v>
@@ -780,22 +947,22 @@
       <c r="I13" s="10"/>
       <c r="J13" s="11"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="6">
+    <row r="14" spans="1:19">
+      <c r="A14" s="12">
         <v>800</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="8"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" spans="1:19">
+      <c r="A15" s="12"/>
       <c r="B15" s="9" t="e">
         <f>SUM(B14:D14)/COUNT(B14:D14)</f>
         <v>#DIV/0!</v>
@@ -814,24 +981,24 @@
       </c>
       <c r="I15" s="10"/>
       <c r="J15" s="11"/>
-      <c r="L15" s="16"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="12">
+      <c r="L15" s="8"/>
+    </row>
+    <row r="16" spans="1:19">
+      <c r="A16" s="13">
         <v>1000</v>
       </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="14"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="12"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="6"/>
+    </row>
+    <row r="17" spans="1:22">
+      <c r="A17" s="13"/>
       <c r="B17" s="9" t="e">
         <f>SUM(B16:D16)/COUNT(B16:D16)</f>
         <v>#DIV/0!</v>
@@ -851,7 +1018,7 @@
       <c r="I17" s="10"/>
       <c r="J17" s="11"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -860,7 +1027,7 @@
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -869,44 +1036,75 @@
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
     </row>
+    <row r="20" spans="1:22">
+      <c r="V20" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="62">
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="H13:J13"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="E15:G15"/>
     <mergeCell ref="H15:J15"/>
     <mergeCell ref="B17:D17"/>
     <mergeCell ref="E17:G17"/>
     <mergeCell ref="H17:J17"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="E13:G13"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>